--- a/data/supplementary/Supplementary_Data_2.xlsx
+++ b/data/supplementary/Supplementary_Data_2.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>S12B and Supplementary Figure S1 report raw D1-D7 domain summaries from the same blinded expert-rating round as the final DGQC endpoint. Reconstructed reviewer-mean DGQC values are 72.56 (full), 72.82 (Stage 1), and 71.37 (Stage 2).</t>
+          <t>S12B and Supplementary Figure S1 report descriptive D1-D7 domain means from the same blinded expert-rating round as the final DGQC score; they are not a separate continuous endpoint.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Raw rating records</t>
+          <t>Expert rating records</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>1,512 ratings from one expert-rating round (46 x 12 + 80 x 12)</t>
+          <t>1,512 blinded ratings from one expert-rating round (46 x 12 + 80 x 12)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Dual-expert adjudication cases</t>
+          <t>Senior-review cases</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Expert review cases retained for the critical-defect endpoint</t>
+          <t>Cases reviewed independently only for the critical-defect endpoint</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Mean DGQC</t>
+          <t>Mean final DGQC score</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Median DGQC</t>
+          <t>Median final DGQC score</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -1000,37 +1000,37 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>D1 raw mean</t>
+          <t>D1 mean</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>D2 raw mean</t>
+          <t>D2 mean</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>D3 raw mean</t>
+          <t>D3 mean</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>D4 raw mean</t>
+          <t>D4 mean</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>D5 raw mean</t>
+          <t>D5 mean</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>D6 raw mean</t>
+          <t>D6 mean</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>D7 raw mean</t>
+          <t>D7 mean</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Mean DGQC</t>
+          <t>Mean final DGQC score</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Median DGQC</t>
+          <t>Median final DGQC score</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
